--- a/publication_tables/supplementary/S8_configuration_results.xlsx
+++ b/publication_tables/supplementary/S8_configuration_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,34 +491,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.1736121747</v>
+        <v>24.17361217469367</v>
       </c>
       <c r="D2" t="n">
-        <v>7.72099842616</v>
+        <v>7.720998426161592</v>
       </c>
       <c r="E2" t="n">
-        <v>3.60538249012</v>
+        <v>3.605382490121753</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.87746566886e-14</v>
+        <v>-1.761018326414436e-14</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.42550461511e-14</v>
+        <v>-1.138025379981973e-14</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.43341393955e-10</v>
+        <v>1.433513260675571e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.400478879599</v>
+        <v>0.4004788795992049</v>
       </c>
     </row>
     <row r="3">
@@ -533,34 +533,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D3" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E3" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="4">
@@ -575,34 +575,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.557174764</v>
+        <v>23.57882188384849</v>
       </c>
       <c r="D4" t="n">
-        <v>7.21456921369</v>
+        <v>7.220856983793082</v>
       </c>
       <c r="E4" t="n">
-        <v>3.23530618598</v>
+        <v>3.238309712598473</v>
       </c>
       <c r="F4" t="n">
-        <v>2.26188565834</v>
+        <v>2.229091928501387</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.893612349065</v>
+        <v>-0.9203494029995636</v>
       </c>
       <c r="H4" t="n">
-        <v>5.39346755406</v>
+        <v>5.70700918541707</v>
       </c>
       <c r="I4" t="n">
-        <v>0.168718799193</v>
+        <v>0.2094720644353072</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.394764010794</v>
+        <v>0.3947878001027232</v>
       </c>
     </row>
     <row r="5">
@@ -617,34 +617,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.0517869305</v>
+        <v>24.08555266842837</v>
       </c>
       <c r="D5" t="n">
-        <v>7.33756984026</v>
+        <v>7.343969389567907</v>
       </c>
       <c r="E5" t="n">
-        <v>3.28864919414</v>
+        <v>3.291691430555442</v>
       </c>
       <c r="F5" t="n">
-        <v>1.10976247066</v>
+        <v>1.077504418528695</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8932020649770001</v>
+        <v>-0.9199436667357968</v>
       </c>
       <c r="H5" t="n">
-        <v>29.9466907135</v>
+        <v>30.06239298366212</v>
       </c>
       <c r="I5" t="n">
-        <v>0.177636894028</v>
+        <v>0.1748805127934855</v>
       </c>
       <c r="J5" t="n">
-        <v>1.55431223448e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.395792151785</v>
+        <v>0.3958154625442059</v>
       </c>
     </row>
     <row r="6">
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.4413624382</v>
+        <v>24.45347239312542</v>
       </c>
       <c r="D6" t="n">
-        <v>7.72523275207</v>
+        <v>7.731657538654853</v>
       </c>
       <c r="E6" t="n">
-        <v>3.55872365005</v>
+        <v>3.561854017177356</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.250257235465</v>
+        <v>-0.2817783294058053</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.890668060596</v>
+        <v>-0.9174248743812805</v>
       </c>
       <c r="H6" t="n">
-        <v>47.2118384312</v>
+        <v>48.17026952202748</v>
       </c>
       <c r="I6" t="n">
-        <v>0.146145315866</v>
+        <v>0.1273996634505085</v>
       </c>
       <c r="J6" t="n">
-        <v>2.22044604925e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.398637349043</v>
+        <v>0.3986603568106426</v>
       </c>
     </row>
     <row r="7">
@@ -701,34 +701,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.4759450361</v>
+        <v>24.4759450360823</v>
       </c>
       <c r="D7" t="n">
-        <v>7.83381662796</v>
+        <v>7.835895213132503</v>
       </c>
       <c r="E7" t="n">
-        <v>3.65638387092</v>
+        <v>3.657417658007697</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.703091646905</v>
+        <v>-0.7160148336489793</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.881111257089</v>
+        <v>-0.893054988761786</v>
       </c>
       <c r="H7" t="n">
-        <v>85.024899408</v>
+        <v>85.79907123733406</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0951022213208</v>
+        <v>0.1663486893538007</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.399942424002</v>
+        <v>0.399941048335793</v>
       </c>
     </row>
     <row r="8">
@@ -743,34 +743,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24.6561062353</v>
+        <v>24.64590407893684</v>
       </c>
       <c r="D8" t="n">
-        <v>7.91845200462</v>
+        <v>7.923790246059456</v>
       </c>
       <c r="E8" t="n">
-        <v>3.70993110994</v>
+        <v>3.712626735638452</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.999106582573</v>
+        <v>-1.022258120774409</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.703923018286</v>
+        <v>-0.7202433258938552</v>
       </c>
       <c r="H8" t="n">
-        <v>99.2189438624</v>
+        <v>98.90904660208646</v>
       </c>
       <c r="I8" t="n">
-        <v>0.063053570743</v>
+        <v>0.1067968060827649</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.401501135182</v>
+        <v>0.4015352542224253</v>
       </c>
     </row>
     <row r="9">
@@ -785,34 +785,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.0126770112</v>
+        <v>23.0174206353949</v>
       </c>
       <c r="D9" t="n">
-        <v>7.06710154085</v>
+        <v>7.07269920725386</v>
       </c>
       <c r="E9" t="n">
-        <v>3.16620600077</v>
+        <v>3.168980376190649</v>
       </c>
       <c r="F9" t="n">
-        <v>3.21166921151</v>
+        <v>3.184654688711239</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0829030454764</v>
+        <v>0.06537254622028371</v>
       </c>
       <c r="H9" t="n">
-        <v>0.696458892421</v>
+        <v>0.7222144106480121</v>
       </c>
       <c r="I9" t="n">
-        <v>0.170113554821</v>
+        <v>0.1781824610566509</v>
       </c>
       <c r="J9" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.39499228781</v>
+        <v>0.3950310526279317</v>
       </c>
     </row>
     <row r="10">
@@ -827,34 +827,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.472179093</v>
+        <v>23.48498411181043</v>
       </c>
       <c r="D10" t="n">
-        <v>7.18714580074</v>
+        <v>7.192813867174555</v>
       </c>
       <c r="E10" t="n">
-        <v>3.21818760107</v>
+        <v>3.220978472673867</v>
       </c>
       <c r="F10" t="n">
-        <v>2.04809144603</v>
+        <v>2.021727624078814</v>
       </c>
       <c r="G10" t="n">
-        <v>0.083468232138</v>
+        <v>0.06593486424949233</v>
       </c>
       <c r="H10" t="n">
-        <v>27.3145688301</v>
+        <v>27.00794280303364</v>
       </c>
       <c r="I10" t="n">
-        <v>0.178787685622</v>
+        <v>0.1446825688737897</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.396020873422</v>
+        <v>0.3960588933852032</v>
       </c>
     </row>
     <row r="11">
@@ -869,34 +869,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.0423730359</v>
+        <v>24.05498314193104</v>
       </c>
       <c r="D11" t="n">
-        <v>7.57316952794</v>
+        <v>7.578787034761689</v>
       </c>
       <c r="E11" t="n">
-        <v>3.48611507876</v>
+        <v>3.488946544737766</v>
       </c>
       <c r="F11" t="n">
-        <v>0.675544892432</v>
+        <v>0.650102711369614</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0862455511457</v>
+        <v>0.06871056883864493</v>
       </c>
       <c r="H11" t="n">
-        <v>11.3802668594</v>
+        <v>12.24384255348039</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1473481175</v>
+        <v>0.09967048554252045</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.398863371683</v>
+        <v>0.398900524942768</v>
       </c>
     </row>
     <row r="12">
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.1105614993</v>
+        <v>24.11056149930288</v>
       </c>
       <c r="D12" t="n">
-        <v>7.68227815801</v>
+        <v>7.68293316854776</v>
       </c>
       <c r="E12" t="n">
-        <v>3.58351978024</v>
+        <v>3.583870278433551</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21788317639</v>
+        <v>0.2139891280469069</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09540312390190001</v>
+        <v>0.09262239100870223</v>
       </c>
       <c r="H12" t="n">
-        <v>38.7363279232</v>
+        <v>38.85905088181479</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0967246157166</v>
+        <v>0.1288998965099755</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.400165537464</v>
+        <v>0.40016747044725</v>
       </c>
     </row>
     <row r="13">
@@ -953,34 +953,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.6323574036</v>
+        <v>24.63651301825862</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8738371728</v>
+        <v>7.875287483341487</v>
       </c>
       <c r="E13" t="n">
-        <v>3.67908877958</v>
+        <v>3.679710541362508</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.923877639855</v>
+        <v>-0.9337973981726565</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.979408456313</v>
+        <v>-0.9915016367112037</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00123897056966</v>
+        <v>0.07013221845544843</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6645352591e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.400259368112</v>
+        <v>0.4002485330386243</v>
       </c>
     </row>
     <row r="14">
@@ -995,34 +995,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9949523773</v>
+        <v>22.99495237732894</v>
       </c>
       <c r="D14" t="n">
-        <v>7.01649956342</v>
+        <v>7.017203704947693</v>
       </c>
       <c r="E14" t="n">
-        <v>3.13328551971</v>
+        <v>3.133425359228792</v>
       </c>
       <c r="F14" t="n">
-        <v>3.32133798132</v>
+        <v>3.314406734829837</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.185418625029</v>
+        <v>-0.1972937693552202</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1780333205</v>
+        <v>1.218552595671547</v>
       </c>
       <c r="I14" t="n">
-        <v>0.116155683358</v>
+        <v>0.172162304827885</v>
       </c>
       <c r="J14" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.220446049250313e-15</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.393687341904</v>
+        <v>0.3936711342800996</v>
       </c>
     </row>
     <row r="15">
@@ -1037,34 +1037,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5038507433</v>
+        <v>23.52849478452226</v>
       </c>
       <c r="D15" t="n">
-        <v>7.13661043304</v>
+        <v>7.137500586161133</v>
       </c>
       <c r="E15" t="n">
-        <v>3.18560477584</v>
+        <v>3.185830567766075</v>
       </c>
       <c r="F15" t="n">
-        <v>2.15082014368</v>
+        <v>2.142776074766308</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.185092283054</v>
+        <v>-0.1969796843580275</v>
       </c>
       <c r="H15" t="n">
-        <v>27.8665240627</v>
+        <v>27.8759044238592</v>
       </c>
       <c r="I15" t="n">
-        <v>0.151926727909</v>
+        <v>0.1887718507935633</v>
       </c>
       <c r="J15" t="n">
-        <v>1.11022302463e-15</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.394728407966</v>
+        <v>0.3947134987971004</v>
       </c>
     </row>
     <row r="16">
@@ -1079,34 +1079,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.9758281113</v>
+        <v>23.97582811132902</v>
       </c>
       <c r="D16" t="n">
-        <v>7.52630129108</v>
+        <v>7.527565899446078</v>
       </c>
       <c r="E16" t="n">
-        <v>3.45417806973</v>
+        <v>3.454665161544809</v>
       </c>
       <c r="F16" t="n">
-        <v>0.765593546915</v>
+        <v>0.7563060379324811</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.184041949796</v>
+        <v>-0.1959634209412746</v>
       </c>
       <c r="H16" t="n">
-        <v>10.6656326475</v>
+        <v>11.05468848400958</v>
       </c>
       <c r="I16" t="n">
-        <v>0.111365865119</v>
+        <v>0.1457242774810106</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.397596698939</v>
+        <v>0.3975846130661453</v>
       </c>
     </row>
     <row r="17">
@@ -1121,34 +1121,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.0217254644</v>
+        <v>24.00560824369576</v>
       </c>
       <c r="D17" t="n">
-        <v>7.63635358195</v>
+        <v>7.632626120889933</v>
       </c>
       <c r="E17" t="n">
-        <v>3.55235507258</v>
+        <v>3.550382873334145</v>
       </c>
       <c r="F17" t="n">
-        <v>0.305923909561</v>
+        <v>0.3187909297893169</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.17414598893</v>
+        <v>-0.1697744548490382</v>
       </c>
       <c r="H17" t="n">
-        <v>28.7247341051</v>
+        <v>26.94414244897174</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0309880124369</v>
+        <v>0.1679693490197965</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.398919666223</v>
+        <v>0.3988783395832611</v>
       </c>
     </row>
     <row r="18">
@@ -1163,34 +1163,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.689584967</v>
+        <v>24.68958496704437</v>
       </c>
       <c r="D18" t="n">
-        <v>7.9139779313</v>
+        <v>7.916776752399171</v>
       </c>
       <c r="E18" t="n">
-        <v>3.70364303165</v>
+        <v>3.705014184745439</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.05941047496</v>
+        <v>-1.072392626575258</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.926139318025</v>
+        <v>-0.936761483010787</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I18" t="n">
-        <v>0.033895286936</v>
+        <v>0.07675296483305147</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.400920971015</v>
+        <v>0.4009332747430954</v>
       </c>
     </row>
     <row r="19">
@@ -1205,34 +1205,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.0488623691</v>
+        <v>23.08207933156254</v>
       </c>
       <c r="D19" t="n">
-        <v>7.05910389601</v>
+        <v>7.061684839680267</v>
       </c>
       <c r="E19" t="n">
-        <v>3.15837598517</v>
+        <v>3.159588382059023</v>
       </c>
       <c r="F19" t="n">
-        <v>3.16275099194</v>
+        <v>3.149314266149048</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.136833110876</v>
+        <v>-0.1479539588064202</v>
       </c>
       <c r="H19" t="n">
-        <v>0.906091737435</v>
+        <v>0.9060917374347153</v>
       </c>
       <c r="I19" t="n">
-        <v>0.145205003906</v>
+        <v>0.1651617311061319</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.394383295234</v>
+        <v>0.3943955263015981</v>
       </c>
     </row>
     <row r="20">
@@ -1247,34 +1247,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.5072457565</v>
+        <v>23.54046271894461</v>
       </c>
       <c r="D20" t="n">
-        <v>7.17943415951</v>
+        <v>7.182124374809301</v>
       </c>
       <c r="E20" t="n">
-        <v>3.21064789965</v>
+        <v>3.21190312318591</v>
       </c>
       <c r="F20" t="n">
-        <v>1.99724076528</v>
+        <v>1.983575491347541</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.136388475612</v>
+        <v>-0.147515660676759</v>
       </c>
       <c r="H20" t="n">
-        <v>27.6722093849</v>
+        <v>27.65632072878571</v>
       </c>
       <c r="I20" t="n">
-        <v>0.162892881437</v>
+        <v>0.1526683869209356</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.39541749169</v>
+        <v>0.3954299453231513</v>
       </c>
     </row>
     <row r="21">
@@ -1289,34 +1289,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.0750604541</v>
+        <v>24.07506045412759</v>
       </c>
       <c r="D21" t="n">
-        <v>7.56762081347</v>
+        <v>7.570490632983487</v>
       </c>
       <c r="E21" t="n">
-        <v>3.47909143949</v>
+        <v>3.480481236806136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.620306999399</v>
+        <v>0.6064887127119668</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.134403423136</v>
+        <v>-0.1455468222546528</v>
       </c>
       <c r="H21" t="n">
-        <v>12.7877607332</v>
+        <v>13.32442793442551</v>
       </c>
       <c r="I21" t="n">
-        <v>0.126518828541</v>
+        <v>0.1070240891727832</v>
       </c>
       <c r="J21" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.398271828188</v>
+        <v>0.3982851463971897</v>
       </c>
     </row>
     <row r="22">
@@ -1331,34 +1331,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1317422922</v>
+        <v>24.13174229221998</v>
       </c>
       <c r="D22" t="n">
-        <v>7.6770964354</v>
+        <v>7.675047306973154</v>
       </c>
       <c r="E22" t="n">
-        <v>3.57686459065</v>
+        <v>3.575824051244943</v>
       </c>
       <c r="F22" t="n">
-        <v>0.162239101994</v>
+        <v>0.1699012573919645</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.124879216563</v>
+        <v>-0.1205823454487627</v>
       </c>
       <c r="H22" t="n">
-        <v>38.8111817107</v>
+        <v>37.46794225555507</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0669044732778</v>
+        <v>0.1433085222158358</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.39958347676</v>
+        <v>0.3995654197113971</v>
       </c>
     </row>
     <row r="23">
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.4912867353</v>
+        <v>25.49328085262495</v>
       </c>
       <c r="D23" t="n">
-        <v>8.315252387359999</v>
+        <v>8.328401085329</v>
       </c>
       <c r="E23" t="n">
-        <v>3.91053519888</v>
+        <v>3.917123475370957</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.18344958758</v>
+        <v>-3.247354766711025</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.80150938598</v>
+        <v>-2.860143314973263</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I23" t="n">
-        <v>0.103201710163</v>
+        <v>0.2343496814488526</v>
       </c>
       <c r="J23" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.401803400547</v>
+        <v>0.4018336454836224</v>
       </c>
     </row>
     <row r="24">
@@ -1415,34 +1415,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.2323522455</v>
+        <v>24.25929889837527</v>
       </c>
       <c r="D24" t="n">
-        <v>7.4544541189</v>
+        <v>7.468348847182229</v>
       </c>
       <c r="E24" t="n">
-        <v>3.35462503811</v>
+        <v>3.361289153814709</v>
       </c>
       <c r="F24" t="n">
-        <v>0.911733130809</v>
+        <v>0.8399147765999264</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.03649252105</v>
+        <v>-2.097123114717066</v>
       </c>
       <c r="H24" t="n">
-        <v>21.0388339995</v>
+        <v>22.6466963215032</v>
       </c>
       <c r="I24" t="n">
-        <v>0.205245240771</v>
+        <v>0.2786996666949718</v>
       </c>
       <c r="J24" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.395329655509</v>
+        <v>0.3953681035560055</v>
       </c>
     </row>
     <row r="25">
@@ -1457,34 +1457,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.7426175474</v>
+        <v>24.76426189978374</v>
       </c>
       <c r="D25" t="n">
-        <v>7.58203028852</v>
+        <v>7.596065299342705</v>
       </c>
       <c r="E25" t="n">
-        <v>3.40964705823</v>
+        <v>3.416361095377557</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.220380597437</v>
+        <v>-0.2904054624712666</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.03613979534</v>
+        <v>-2.096773493599852</v>
       </c>
       <c r="H25" t="n">
-        <v>38.9739204582</v>
+        <v>39.81854877247417</v>
       </c>
       <c r="I25" t="n">
-        <v>0.209973537309</v>
+        <v>0.2302735372053213</v>
       </c>
       <c r="J25" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.396348680587</v>
+        <v>0.3963856054347179</v>
       </c>
     </row>
     <row r="26">
@@ -1499,34 +1499,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.9371330863</v>
+        <v>24.99811182019034</v>
       </c>
       <c r="D26" t="n">
-        <v>7.9680269834</v>
+        <v>7.981715224806942</v>
       </c>
       <c r="E26" t="n">
-        <v>3.68209353853</v>
+        <v>3.688841659108168</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.55519326258</v>
+        <v>-1.62303692953782</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.03282419802</v>
+        <v>-2.093479514295701</v>
       </c>
       <c r="H26" t="n">
-        <v>80.2330055004</v>
+        <v>81.10106004123473</v>
       </c>
       <c r="I26" t="n">
-        <v>0.180479466003</v>
+        <v>0.1919512682137304</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.220446049250313e-15</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.399180139415</v>
+        <v>0.3992150127308787</v>
       </c>
     </row>
     <row r="27">
@@ -1541,34 +1541,34 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.0282856341</v>
+        <v>25.05832473950338</v>
       </c>
       <c r="D27" t="n">
-        <v>8.07502549624</v>
+        <v>8.085211377737057</v>
       </c>
       <c r="E27" t="n">
-        <v>3.77957725032</v>
+        <v>3.784722758730114</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.00027428857</v>
+        <v>-2.053512267511761</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.02323334742</v>
+        <v>-2.069918269416135</v>
       </c>
       <c r="H27" t="n">
-        <v>98.8009938103</v>
+        <v>98.79336641942339</v>
       </c>
       <c r="I27" t="n">
-        <v>0.13770193776</v>
+        <v>0.2307472079670358</v>
       </c>
       <c r="J27" t="n">
-        <v>2.22044604925e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.400476122589</v>
+        <v>0.4004967053983244</v>
       </c>
     </row>
     <row r="28">
@@ -1583,34 +1583,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D28" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E28" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J28" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="29">
@@ -1625,34 +1625,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2768695446</v>
+        <v>24.27962803653804</v>
       </c>
       <c r="D29" t="n">
-        <v>7.63655941754</v>
+        <v>7.642806177424324</v>
       </c>
       <c r="E29" t="n">
-        <v>3.50203189394</v>
+        <v>3.50505427430394</v>
       </c>
       <c r="F29" t="n">
-        <v>0.178067526422</v>
+        <v>0.1470019860867246</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.28307787345</v>
+        <v>-1.309265099670023</v>
       </c>
       <c r="H29" t="n">
-        <v>31.4973153723</v>
+        <v>32.51101002942877</v>
       </c>
       <c r="I29" t="n">
-        <v>0.11206125296</v>
+        <v>0.1562697841332248</v>
       </c>
       <c r="J29" t="n">
-        <v>1.33226762955e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.398005908621</v>
+        <v>0.3980279644098328</v>
       </c>
     </row>
     <row r="30">
@@ -1667,34 +1667,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5370550713</v>
+        <v>24.54151296448633</v>
       </c>
       <c r="D30" t="n">
-        <v>7.70034371704</v>
+        <v>7.706632068618552</v>
       </c>
       <c r="E30" t="n">
-        <v>3.52974476129</v>
+        <v>3.532788793667749</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.398582092171</v>
+        <v>-0.4294066919306888</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.28289541833</v>
+        <v>-1.309085947238809</v>
       </c>
       <c r="H30" t="n">
-        <v>45.4032866314</v>
+        <v>46.25864779455092</v>
       </c>
       <c r="I30" t="n">
-        <v>0.114247937199</v>
+        <v>0.1307104288248414</v>
       </c>
       <c r="J30" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.398515470429</v>
+        <v>0.3985373261996117</v>
       </c>
     </row>
     <row r="31">
@@ -1709,34 +1709,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7603580561</v>
+        <v>24.7872463685314</v>
       </c>
       <c r="D31" t="n">
-        <v>7.89786997894</v>
+        <v>7.904196394273408</v>
       </c>
       <c r="E31" t="n">
-        <v>3.67045731918</v>
+        <v>3.673546254541381</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.07926152671</v>
+        <v>-1.109748527205086</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.28168312137</v>
+        <v>-1.30788383918538</v>
       </c>
       <c r="H31" t="n">
-        <v>86.3609705595</v>
+        <v>86.74132913360387</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09939127740299999</v>
+        <v>0.112900076789218</v>
       </c>
       <c r="J31" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.399951748379</v>
+        <v>0.3999734933329118</v>
       </c>
     </row>
     <row r="32">
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24.7859662423</v>
+        <v>24.79150973012053</v>
       </c>
       <c r="D32" t="n">
-        <v>7.95132995752</v>
+        <v>7.956369175814447</v>
       </c>
       <c r="E32" t="n">
-        <v>3.71944903591</v>
+        <v>3.721981683792693</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.30178222225</v>
+        <v>-1.327430697765371</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.27393236636</v>
+        <v>-1.295358271609151</v>
       </c>
       <c r="H32" t="n">
-        <v>99.28641059829999</v>
+        <v>99.26950798259105</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0783449154375</v>
+        <v>0.1301486599730747</v>
       </c>
       <c r="J32" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.400599683245</v>
+        <v>0.4006151968091052</v>
       </c>
     </row>
     <row r="33">
@@ -1793,34 +1793,34 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D33" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E33" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J33" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="34">
@@ -1835,34 +1835,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>21.8721734162</v>
+        <v>21.87217341623418</v>
       </c>
       <c r="D34" t="n">
-        <v>6.41507746304</v>
+        <v>6.421378405284803</v>
       </c>
       <c r="E34" t="n">
-        <v>2.74782142702</v>
+        <v>2.750804576505972</v>
       </c>
       <c r="F34" t="n">
-        <v>6.41882974802</v>
+        <v>6.382077549948684</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.116580104531</v>
+        <v>-0.1445104043417993</v>
       </c>
       <c r="H34" t="n">
-        <v>0.711035150318</v>
+        <v>0.7327613046983672</v>
       </c>
       <c r="I34" t="n">
-        <v>0.282252920783</v>
+        <v>0.3164345386645322</v>
       </c>
       <c r="J34" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.388366838151</v>
+        <v>0.3883947633150233</v>
       </c>
     </row>
     <row r="35">
@@ -1877,34 +1877,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22.6736053153</v>
+        <v>22.67360531532245</v>
       </c>
       <c r="D35" t="n">
-        <v>6.64750785619</v>
+        <v>6.653939371158274</v>
       </c>
       <c r="E35" t="n">
-        <v>2.84671210399</v>
+        <v>2.849759078761315</v>
       </c>
       <c r="F35" t="n">
-        <v>4.119260427</v>
+        <v>4.083794502411429</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.115579161121</v>
+        <v>-0.1435103907892765</v>
       </c>
       <c r="H35" t="n">
-        <v>27.5798719389</v>
+        <v>27.57987193885789</v>
       </c>
       <c r="I35" t="n">
-        <v>0.319474704766</v>
+        <v>0.2991734506325572</v>
       </c>
       <c r="J35" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.390457201948</v>
+        <v>0.3904838518935576</v>
       </c>
     </row>
     <row r="36">
@@ -1919,34 +1919,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>23.8283626183</v>
+        <v>23.83014831820558</v>
       </c>
       <c r="D36" t="n">
-        <v>7.38706252909</v>
+        <v>7.393689928100721</v>
       </c>
       <c r="E36" t="n">
-        <v>3.34307502791</v>
+        <v>3.346294758777632</v>
       </c>
       <c r="F36" t="n">
-        <v>1.40454725355</v>
+        <v>1.370802147828383</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1100760986</v>
+        <v>-0.1380171981794113</v>
       </c>
       <c r="H36" t="n">
-        <v>10.4878717838</v>
+        <v>10.97740642946058</v>
       </c>
       <c r="I36" t="n">
-        <v>0.246336461919</v>
+        <v>0.209879368392255</v>
       </c>
       <c r="J36" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.396038289008</v>
+        <v>0.3960640108532665</v>
       </c>
     </row>
     <row r="37">
@@ -1961,34 +1961,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>24.0304923243</v>
+        <v>24.02617019414537</v>
       </c>
       <c r="D37" t="n">
-        <v>7.60920295068</v>
+        <v>7.600540115658322</v>
       </c>
       <c r="E37" t="n">
-        <v>3.53679199141</v>
+        <v>3.532256862690042</v>
       </c>
       <c r="F37" t="n">
-        <v>0.468805091461</v>
+        <v>0.5066790887281827</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.113879726734</v>
+        <v>-0.09206773914597691</v>
       </c>
       <c r="H37" t="n">
-        <v>34.0471538712</v>
+        <v>30.85263387313222</v>
       </c>
       <c r="I37" t="n">
-        <v>0.128363351959</v>
+        <v>0.2834361829843837</v>
       </c>
       <c r="J37" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.398682443211</v>
+        <v>0.3986148798612343</v>
       </c>
     </row>
     <row r="38">
@@ -2003,34 +2003,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25.0225677011</v>
+        <v>25.03341590627914</v>
       </c>
       <c r="D38" t="n">
-        <v>8.08442172945</v>
+        <v>8.090743654395602</v>
       </c>
       <c r="E38" t="n">
-        <v>3.79100660546</v>
+        <v>3.794123623129922</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.98174965164</v>
+        <v>-2.012452825953441</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.73906681114</v>
+        <v>-1.76611090235712</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0426482168897</v>
+        <v>0.1313961034513512</v>
       </c>
       <c r="J38" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>4.440892098500626e-15</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.401281698475</v>
+        <v>0.4013009397195342</v>
       </c>
     </row>
     <row r="39">
@@ -2045,34 +2045,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>23.5656822293</v>
+        <v>23.58732934910219</v>
       </c>
       <c r="D39" t="n">
-        <v>7.22440109164</v>
+        <v>7.230813619199485</v>
       </c>
       <c r="E39" t="n">
-        <v>3.24006357854</v>
+        <v>3.243119753884613</v>
       </c>
       <c r="F39" t="n">
-        <v>2.19507781958</v>
+        <v>2.161126140039159</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9580891016800001</v>
+        <v>-0.9861756845454011</v>
       </c>
       <c r="H39" t="n">
-        <v>6.1381338519</v>
+        <v>6.427464423764671</v>
       </c>
       <c r="I39" t="n">
-        <v>0.152591089603</v>
+        <v>0.2022368225802352</v>
       </c>
       <c r="J39" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.394756694135</v>
+        <v>0.3947790326814384</v>
       </c>
     </row>
     <row r="40">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>24.0717210306</v>
+        <v>24.09682603920302</v>
       </c>
       <c r="D40" t="n">
-        <v>7.34791489952</v>
+        <v>7.354445353848576</v>
       </c>
       <c r="E40" t="n">
-        <v>3.29363370595</v>
+        <v>3.296731862395297</v>
       </c>
       <c r="F40" t="n">
-        <v>1.04159384577</v>
+        <v>1.008175805611776</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.957679897403</v>
+        <v>-0.9857710718236786</v>
       </c>
       <c r="H40" t="n">
-        <v>30.3898826095</v>
+        <v>30.49306543827868</v>
       </c>
       <c r="I40" t="n">
-        <v>0.166906160076</v>
+        <v>0.1663297294022746</v>
       </c>
       <c r="J40" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.395787269402</v>
+        <v>0.3958091635595042</v>
       </c>
     </row>
     <row r="41">
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.481884315</v>
+        <v>24.47595052915026</v>
       </c>
       <c r="D41" t="n">
-        <v>7.73607210264</v>
+        <v>7.742630808040614</v>
       </c>
       <c r="E41" t="n">
-        <v>3.56424638312</v>
+        <v>3.567436731105891</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.319937098951</v>
+        <v>-0.352624780083015</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.955083308918</v>
+        <v>-0.9831909836863391</v>
       </c>
       <c r="H41" t="n">
-        <v>49.3868012651</v>
+        <v>50.55229928824898</v>
       </c>
       <c r="I41" t="n">
-        <v>0.132702432856</v>
+        <v>0.1165395959969815</v>
       </c>
       <c r="J41" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.398637004569</v>
+        <v>0.3986586400780843</v>
       </c>
     </row>
     <row r="42">
@@ -2171,34 +2171,34 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24.4889162214</v>
+        <v>24.49307183605282</v>
       </c>
       <c r="D42" t="n">
-        <v>7.84478927358</v>
+        <v>7.847044518493002</v>
       </c>
       <c r="E42" t="n">
-        <v>3.6620447516</v>
+        <v>3.663166896753509</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.773736506244</v>
+        <v>-0.7878351405830053</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.945901369159</v>
+        <v>-0.9590195657679801</v>
       </c>
       <c r="H42" t="n">
-        <v>90.0209018111</v>
+        <v>90.55341134062621</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0760945033102</v>
+        <v>0.1482775237188609</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.399943004521</v>
+        <v>0.3999412455890348</v>
       </c>
     </row>
     <row r="43">
@@ -2213,34 +2213,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24.9897398198</v>
+        <v>25.02897567361481</v>
       </c>
       <c r="D43" t="n">
-        <v>8.06202978092</v>
+        <v>8.068109289039018</v>
       </c>
       <c r="E43" t="n">
-        <v>3.77932215956</v>
+        <v>3.782339013073026</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.84401261211</v>
+        <v>-1.872751393499986</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.6125464329</v>
+        <v>-1.637219507586855</v>
       </c>
       <c r="H43" t="n">
-        <v>99.8953873462</v>
+        <v>99.7047383980612</v>
       </c>
       <c r="I43" t="n">
-        <v>0.078564321465</v>
+        <v>0.1465652528447669</v>
       </c>
       <c r="J43" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.401275758683</v>
+        <v>0.4012977352619158</v>
       </c>
     </row>
     <row r="44">
@@ -2255,34 +2255,34 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23.5686730385</v>
+        <v>23.57637724595459</v>
       </c>
       <c r="D44" t="n">
-        <v>7.20566766883</v>
+        <v>7.211893081966894</v>
       </c>
       <c r="E44" t="n">
-        <v>3.23102809865</v>
+        <v>3.234012066748501</v>
       </c>
       <c r="F44" t="n">
-        <v>2.32231077568</v>
+        <v>2.290224029517123</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.834133915285</v>
+        <v>-0.8598977271966919</v>
       </c>
       <c r="H44" t="n">
-        <v>4.85380720358</v>
+        <v>5.103683609315109</v>
       </c>
       <c r="I44" t="n">
-        <v>0.18345297376</v>
+        <v>0.2164374481584752</v>
       </c>
       <c r="J44" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.394775035178</v>
+        <v>0.3948004074265323</v>
       </c>
     </row>
     <row r="45">
@@ -2297,34 +2297,34 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>24.0642075543</v>
+        <v>24.0719117617321</v>
       </c>
       <c r="D45" t="n">
-        <v>7.32820850651</v>
+        <v>7.334543634291062</v>
       </c>
       <c r="E45" t="n">
-        <v>3.28416577129</v>
+        <v>3.28718585831683</v>
       </c>
       <c r="F45" t="n">
-        <v>1.17142782016</v>
+        <v>1.139886744216538</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.83371846441</v>
+        <v>-0.8594866473988835</v>
       </c>
       <c r="H45" t="n">
-        <v>29.5884472126</v>
+        <v>29.67669622670055</v>
       </c>
       <c r="I45" t="n">
-        <v>0.189830549998</v>
+        <v>0.1848799652397574</v>
       </c>
       <c r="J45" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.395800944923</v>
+        <v>0.3958258036896103</v>
       </c>
     </row>
     <row r="46">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24.4400292171</v>
+        <v>24.4482205100667</v>
       </c>
       <c r="D46" t="n">
-        <v>7.71542186144</v>
+        <v>7.721782270803634</v>
       </c>
       <c r="E46" t="n">
-        <v>3.55374982952</v>
+        <v>3.556854056775881</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.187210117738</v>
+        <v>-0.2179985073448774</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.831232196298</v>
+        <v>-0.8570141167171286</v>
       </c>
       <c r="H46" t="n">
-        <v>45.0547380532</v>
+        <v>45.54891742199823</v>
       </c>
       <c r="I46" t="n">
-        <v>0.159278277673</v>
+        <v>0.139827735381385</v>
       </c>
       <c r="J46" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.398641979181</v>
+        <v>0.3986664807935423</v>
       </c>
     </row>
     <row r="47">
@@ -2381,34 +2381,34 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.4515295094</v>
+        <v>24.42687005764223</v>
       </c>
       <c r="D47" t="n">
-        <v>7.82391253115</v>
+        <v>7.825864018404867</v>
       </c>
       <c r="E47" t="n">
-        <v>3.65129114334</v>
+        <v>3.65226827738207</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.639269717963</v>
+        <v>-0.6513908987594856</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.821404733019</v>
+        <v>-0.8324886369367543</v>
       </c>
       <c r="H47" t="n">
-        <v>80.97021794139999</v>
+        <v>81.68867632301514</v>
       </c>
       <c r="I47" t="n">
-        <v>0.112301638751</v>
+        <v>0.1829548142569538</v>
       </c>
       <c r="J47" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.399946246244</v>
+        <v>0.3999454172259291</v>
       </c>
     </row>
     <row r="48">
@@ -2423,34 +2423,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25.0304979622</v>
+        <v>25.04790549819274</v>
       </c>
       <c r="D48" t="n">
-        <v>8.078257188829999</v>
+        <v>8.0858724853094</v>
       </c>
       <c r="E48" t="n">
-        <v>3.78769253758</v>
+        <v>3.791473603293947</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.93200202599</v>
+        <v>-1.967246466361872</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.68893246807</v>
+        <v>-1.718596969299547</v>
       </c>
       <c r="H48" t="n">
-        <v>99.90696106</v>
+        <v>99.7047383980612</v>
       </c>
       <c r="I48" t="n">
-        <v>0.07860828296029999</v>
+        <v>0.1519745146038512</v>
       </c>
       <c r="J48" t="n">
-        <v>1.55431223448e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.401314021895</v>
+        <v>0.4013443719598508</v>
       </c>
     </row>
     <row r="49">
@@ -2465,34 +2465,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23.5806319806</v>
+        <v>23.58063198062023</v>
       </c>
       <c r="D49" t="n">
-        <v>7.2165818077</v>
+        <v>7.224119849724852</v>
       </c>
       <c r="E49" t="n">
-        <v>3.23565635751</v>
+        <v>3.239244558994526</v>
       </c>
       <c r="F49" t="n">
-        <v>2.25533106755</v>
+        <v>2.217085375870774</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.90900740485</v>
+        <v>-0.9399674462054474</v>
       </c>
       <c r="H49" t="n">
-        <v>5.51083967378</v>
+        <v>5.731766183431069</v>
       </c>
       <c r="I49" t="n">
-        <v>0.187801694704</v>
+        <v>0.2233903292785884</v>
       </c>
       <c r="J49" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.394775934991</v>
+        <v>0.3948088518944814</v>
       </c>
     </row>
     <row r="50">
@@ -2507,34 +2507,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24.0855526684</v>
+        <v>24.08555266842837</v>
       </c>
       <c r="D50" t="n">
-        <v>7.34055908591</v>
+        <v>7.348289669388721</v>
       </c>
       <c r="E50" t="n">
-        <v>3.28946802341</v>
+        <v>3.293129618388494</v>
       </c>
       <c r="F50" t="n">
-        <v>1.09618214002</v>
+        <v>1.058132239839785</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.908720815393</v>
+        <v>-0.9396948318531039</v>
       </c>
       <c r="H50" t="n">
-        <v>29.9335936694</v>
+        <v>29.96980365904885</v>
       </c>
       <c r="I50" t="n">
-        <v>0.19357441464</v>
+        <v>0.190227084197044</v>
       </c>
       <c r="J50" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.395811016963</v>
+        <v>0.3958437459365023</v>
       </c>
     </row>
     <row r="51">
@@ -2549,34 +2549,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>24.4534723931</v>
+        <v>24.53291583894062</v>
       </c>
       <c r="D51" t="n">
-        <v>7.73048216705</v>
+        <v>7.738421427000976</v>
       </c>
       <c r="E51" t="n">
-        <v>3.56111929778</v>
+        <v>3.564984410212046</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.271228338355</v>
+        <v>-0.3088526378701907</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.9064802320599999</v>
+        <v>-0.9374920794275671</v>
       </c>
       <c r="H51" t="n">
-        <v>47.6656301684</v>
+        <v>49.41934697780573</v>
       </c>
       <c r="I51" t="n">
-        <v>0.16235330537</v>
+        <v>0.1453167092475584</v>
       </c>
       <c r="J51" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.398672217663</v>
+        <v>0.398705534361703</v>
       </c>
     </row>
     <row r="52">
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>24.519857324</v>
+        <v>24.52285235912482</v>
       </c>
       <c r="D52" t="n">
-        <v>7.83889230101</v>
+        <v>7.84283382519981</v>
       </c>
       <c r="E52" t="n">
-        <v>3.65881772257</v>
+        <v>3.660845980249163</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.7203084131</v>
+        <v>-0.7427188315508009</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.893592346626</v>
+        <v>-0.9117697430028108</v>
       </c>
       <c r="H52" t="n">
-        <v>82.35327191010001</v>
+        <v>83.79321196732857</v>
       </c>
       <c r="I52" t="n">
-        <v>0.122130740025</v>
+        <v>0.1911756686273096</v>
       </c>
       <c r="J52" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.399982781704</v>
+        <v>0.3999919083046253</v>
       </c>
     </row>
     <row r="53">
@@ -2633,34 +2633,34 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>24.9955616371</v>
+        <v>25.00468814230315</v>
       </c>
       <c r="D53" t="n">
-        <v>8.06905927827</v>
+        <v>8.07439072985626</v>
       </c>
       <c r="E53" t="n">
-        <v>3.78303200138</v>
+        <v>3.785656099517638</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.89477745694</v>
+        <v>-1.920923008410296</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.6630582528</v>
+        <v>-1.686388958006205</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>0.050512058378</v>
+        <v>0.1316242221266553</v>
       </c>
       <c r="J53" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.401252069645</v>
+        <v>0.4012669525008052</v>
       </c>
     </row>
     <row r="54">
@@ -2675,34 +2675,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>23.5067287815</v>
+        <v>23.55717476400687</v>
       </c>
       <c r="D54" t="n">
-        <v>7.21327861117</v>
+        <v>7.218765430191785</v>
       </c>
       <c r="E54" t="n">
-        <v>3.23506914677</v>
+        <v>3.237706885731992</v>
       </c>
       <c r="F54" t="n">
-        <v>2.26625275192</v>
+        <v>2.236859255031303</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.883699425279</v>
+        <v>-0.9079463661652355</v>
       </c>
       <c r="H54" t="n">
-        <v>5.40704150365</v>
+        <v>5.573637429982879</v>
       </c>
       <c r="I54" t="n">
-        <v>0.156608104297</v>
+        <v>0.201380975671482</v>
       </c>
       <c r="J54" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.39475634645</v>
+        <v>0.3947745601071011</v>
       </c>
     </row>
     <row r="55">
@@ -2717,34 +2717,34 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>24.001340948</v>
+        <v>24.05178693046021</v>
       </c>
       <c r="D55" t="n">
-        <v>7.33566936209</v>
+        <v>7.341227062305062</v>
       </c>
       <c r="E55" t="n">
-        <v>3.28811581763</v>
+        <v>3.290776914309903</v>
       </c>
       <c r="F55" t="n">
-        <v>1.11858191692</v>
+        <v>1.089843876932466</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.883211843928</v>
+        <v>-0.9074592053807576</v>
       </c>
       <c r="H55" t="n">
-        <v>30.0247061797</v>
+        <v>30.1004780865127</v>
       </c>
       <c r="I55" t="n">
-        <v>0.168891533903</v>
+        <v>0.1663998564118582</v>
       </c>
       <c r="J55" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.395780086959</v>
+        <v>0.3957977314296903</v>
       </c>
     </row>
     <row r="56">
@@ -2759,34 +2759,34 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>24.4341605681</v>
+        <v>24.4548056142036</v>
       </c>
       <c r="D56" t="n">
-        <v>7.72187154854</v>
+        <v>7.727416193186625</v>
       </c>
       <c r="E56" t="n">
-        <v>3.55718835176</v>
+        <v>3.559885715584062</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.236749572419</v>
+        <v>-0.2646537604382262</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.880494028413</v>
+        <v>-0.9047466140819505</v>
       </c>
       <c r="H56" t="n">
-        <v>46.6152853627</v>
+        <v>47.84642233376722</v>
       </c>
       <c r="I56" t="n">
-        <v>0.136524939178</v>
+        <v>0.1174862674179197</v>
       </c>
       <c r="J56" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.398615109009</v>
+        <v>0.3986320964376571</v>
       </c>
     </row>
     <row r="57">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>24.4791535559</v>
+        <v>24.4841450185825</v>
       </c>
       <c r="D57" t="n">
-        <v>7.83056704624</v>
+        <v>7.83154089105055</v>
       </c>
       <c r="E57" t="n">
-        <v>3.65482210917</v>
+        <v>3.655263649257448</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6918777001550001</v>
+        <v>-0.6991004505882202</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.872997167451</v>
+        <v>-0.8812066629337368</v>
       </c>
       <c r="H57" t="n">
-        <v>87.0300920536</v>
+        <v>87.62724448317432</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0778776993313</v>
+        <v>0.1512217290059223</v>
       </c>
       <c r="J57" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.399916828321</v>
+        <v>0.3999092953292556</v>
       </c>
     </row>
     <row r="58">
@@ -2843,34 +2843,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D58" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E58" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J58" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="59">
@@ -2885,34 +2885,34 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.4888090575</v>
+        <v>23.48880905753004</v>
       </c>
       <c r="D59" t="n">
-        <v>7.18382128617</v>
+        <v>7.189930865138571</v>
       </c>
       <c r="E59" t="n">
-        <v>3.21605602414</v>
+        <v>3.218965353463763</v>
       </c>
       <c r="F59" t="n">
-        <v>2.41659370322</v>
+        <v>2.384403969157464</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.866352536235</v>
+        <v>-0.8930659313678904</v>
       </c>
       <c r="H59" t="n">
-        <v>4.69757913828</v>
+        <v>5.03107185319703</v>
       </c>
       <c r="I59" t="n">
-        <v>0.175182721469</v>
+        <v>0.2148411781883435</v>
       </c>
       <c r="J59" t="n">
-        <v>1.11022302463e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0.394524452437</v>
+        <v>0.3945472704059105</v>
       </c>
     </row>
     <row r="60">
@@ -2927,34 +2927,34 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>24.001340948</v>
+        <v>23.99798448000382</v>
       </c>
       <c r="D60" t="n">
-        <v>7.31118936366</v>
+        <v>7.317439982519548</v>
       </c>
       <c r="E60" t="n">
-        <v>3.27127839134</v>
+        <v>3.274239432234081</v>
       </c>
       <c r="F60" t="n">
-        <v>1.22077009794</v>
+        <v>1.18888790246115</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.865941567192</v>
+        <v>-0.8926613545129781</v>
       </c>
       <c r="H60" t="n">
-        <v>29.5505086791</v>
+        <v>29.69970474649613</v>
       </c>
       <c r="I60" t="n">
-        <v>0.184411068996</v>
+        <v>0.1804603665831012</v>
       </c>
       <c r="J60" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.395592379116</v>
+        <v>0.3956149301846672</v>
       </c>
     </row>
     <row r="61">
@@ -2969,34 +2969,34 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>24.4245092694</v>
+        <v>24.440029217135</v>
       </c>
       <c r="D61" t="n">
-        <v>7.71305035061</v>
+        <v>7.719452815109144</v>
       </c>
       <c r="E61" t="n">
-        <v>3.55075523244</v>
+        <v>3.553862223242159</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.19080394511</v>
+        <v>-0.2222118273046207</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.863343430126</v>
+        <v>-0.8900828048782108</v>
       </c>
       <c r="H61" t="n">
-        <v>44.7737257131</v>
+        <v>45.63674422465239</v>
       </c>
       <c r="I61" t="n">
-        <v>0.151735155289</v>
+        <v>0.1316563318890156</v>
       </c>
       <c r="J61" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.398543614224</v>
+        <v>0.3985664519764907</v>
       </c>
     </row>
     <row r="62">
@@ -3011,34 +3011,34 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>24.4759450361</v>
+        <v>24.4759450360823</v>
       </c>
       <c r="D62" t="n">
-        <v>7.83381662796</v>
+        <v>7.835895213132503</v>
       </c>
       <c r="E62" t="n">
-        <v>3.65638387092</v>
+        <v>3.657417658007697</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.703091646905</v>
+        <v>-0.7160148336489793</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.881111257089</v>
+        <v>-0.893054988761786</v>
       </c>
       <c r="H62" t="n">
-        <v>85.024899408</v>
+        <v>85.79907123733406</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0951022213208</v>
+        <v>0.1663486893538007</v>
       </c>
       <c r="J62" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.399942424002</v>
+        <v>0.399941048335793</v>
       </c>
     </row>
     <row r="63">
@@ -3053,34 +3053,34 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D63" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E63" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G63" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J63" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="64">
@@ -3095,34 +3095,34 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23.6338640369</v>
+        <v>23.63736308465917</v>
       </c>
       <c r="D64" t="n">
-        <v>7.28495275509</v>
+        <v>7.291474839996663</v>
       </c>
       <c r="E64" t="n">
-        <v>3.27954409836</v>
+        <v>3.282735232510322</v>
       </c>
       <c r="F64" t="n">
-        <v>1.90886308019</v>
+        <v>1.874928894801711</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.955807970087</v>
+        <v>-0.9825572996384651</v>
       </c>
       <c r="H64" t="n">
-        <v>6.93821734588</v>
+        <v>7.352089484787307</v>
       </c>
       <c r="I64" t="n">
-        <v>0.153956904935</v>
+        <v>0.1972534021370257</v>
       </c>
       <c r="J64" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.395311140128</v>
+        <v>0.3953367804457204</v>
       </c>
     </row>
     <row r="65">
@@ -3137,34 +3137,34 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>24.098744729</v>
+        <v>24.11006286620561</v>
       </c>
       <c r="D65" t="n">
-        <v>7.397957609</v>
+        <v>7.404526092448415</v>
       </c>
       <c r="E65" t="n">
-        <v>3.3285615804</v>
+        <v>3.331764614547105</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8564420812670001</v>
+        <v>0.8234946559203338</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.955403471592</v>
+        <v>-0.9821536473094861</v>
       </c>
       <c r="H65" t="n">
-        <v>30.7784301467</v>
+        <v>30.97456974260198</v>
       </c>
       <c r="I65" t="n">
-        <v>0.16216512468</v>
+        <v>0.1623493431885506</v>
       </c>
       <c r="J65" t="n">
-        <v>1.33226762955e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.396248718266</v>
+        <v>0.3962734658942249</v>
       </c>
     </row>
     <row r="66">
@@ -3179,34 +3179,34 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>24.5338802758</v>
+        <v>24.5423884340068</v>
       </c>
       <c r="D66" t="n">
-        <v>7.75307722174</v>
+        <v>7.75955497551448</v>
       </c>
       <c r="E66" t="n">
-        <v>3.57695807967</v>
+        <v>3.580130299259033</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.385947868184</v>
+        <v>-0.4176402190485575</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.9530248846129999</v>
+        <v>-0.9797814359911131</v>
       </c>
       <c r="H66" t="n">
-        <v>53.1571242046</v>
+        <v>54.38950583597526</v>
       </c>
       <c r="I66" t="n">
-        <v>0.133379125765</v>
+        <v>0.1183881666107288</v>
       </c>
       <c r="J66" t="n">
-        <v>4.4408920985e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.398851473154</v>
+        <v>0.3988747344666759</v>
       </c>
     </row>
     <row r="67">
@@ -3221,34 +3221,34 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>24.4759450361</v>
+        <v>24.4759450360823</v>
       </c>
       <c r="D67" t="n">
-        <v>7.83381662796</v>
+        <v>7.835895213132503</v>
       </c>
       <c r="E67" t="n">
-        <v>3.65638387092</v>
+        <v>3.657417658007697</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.703091646905</v>
+        <v>-0.7160148336489793</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.881111257089</v>
+        <v>-0.893054988761786</v>
       </c>
       <c r="H67" t="n">
-        <v>85.024899408</v>
+        <v>85.79907123733406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0951022213208</v>
+        <v>0.1663486893538007</v>
       </c>
       <c r="J67" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.399942424002</v>
+        <v>0.399941048335793</v>
       </c>
     </row>
     <row r="68">
@@ -3263,34 +3263,34 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D68" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E68" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J68" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="69">
@@ -3305,34 +3305,34 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>23.557174764</v>
+        <v>23.57882188384849</v>
       </c>
       <c r="D69" t="n">
-        <v>7.21456921369</v>
+        <v>7.220856983793082</v>
       </c>
       <c r="E69" t="n">
-        <v>3.23530618598</v>
+        <v>3.238309712598473</v>
       </c>
       <c r="F69" t="n">
-        <v>2.26188565834</v>
+        <v>2.229091928501387</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.893612349065</v>
+        <v>-0.9203494029995636</v>
       </c>
       <c r="H69" t="n">
-        <v>5.39346755406</v>
+        <v>5.70700918541707</v>
       </c>
       <c r="I69" t="n">
-        <v>0.168718799193</v>
+        <v>0.2094720644353072</v>
       </c>
       <c r="J69" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.394764010794</v>
+        <v>0.3947878001027232</v>
       </c>
     </row>
     <row r="70">
@@ -3347,34 +3347,34 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>24.0517869305</v>
+        <v>24.08555266842837</v>
       </c>
       <c r="D70" t="n">
-        <v>7.33756984026</v>
+        <v>7.343969389567907</v>
       </c>
       <c r="E70" t="n">
-        <v>3.28864919414</v>
+        <v>3.291691430555442</v>
       </c>
       <c r="F70" t="n">
-        <v>1.10976247066</v>
+        <v>1.077504418528695</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.8932020649770001</v>
+        <v>-0.9199436667357968</v>
       </c>
       <c r="H70" t="n">
-        <v>29.9466907135</v>
+        <v>30.06239298366212</v>
       </c>
       <c r="I70" t="n">
-        <v>0.177636894028</v>
+        <v>0.1748805127934855</v>
       </c>
       <c r="J70" t="n">
-        <v>1.55431223448e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0.395792151785</v>
+        <v>0.3958154625442059</v>
       </c>
     </row>
     <row r="71">
@@ -3389,34 +3389,34 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>24.4413624382</v>
+        <v>24.45347239312542</v>
       </c>
       <c r="D71" t="n">
-        <v>7.72523275207</v>
+        <v>7.731657538654853</v>
       </c>
       <c r="E71" t="n">
-        <v>3.55872365005</v>
+        <v>3.561854017177356</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.250257235465</v>
+        <v>-0.2817783294058053</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.890668060596</v>
+        <v>-0.9174248743812805</v>
       </c>
       <c r="H71" t="n">
-        <v>47.2118384312</v>
+        <v>48.17026952202748</v>
       </c>
       <c r="I71" t="n">
-        <v>0.146145315866</v>
+        <v>0.1273996634505085</v>
       </c>
       <c r="J71" t="n">
-        <v>2.22044604925e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.398637349043</v>
+        <v>0.3986603568106426</v>
       </c>
     </row>
     <row r="72">
@@ -3431,34 +3431,34 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>24.5358636404</v>
+        <v>24.54410979461479</v>
       </c>
       <c r="D72" t="n">
-        <v>7.86940247584</v>
+        <v>7.863138329432706</v>
       </c>
       <c r="E72" t="n">
-        <v>3.68081308828</v>
+        <v>3.677895197289109</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.880059657496</v>
+        <v>-0.8395910117743517</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.949244044686</v>
+        <v>-0.9121810981860241</v>
       </c>
       <c r="H72" t="n">
-        <v>84.8531506594</v>
+        <v>83.17014806399105</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0772382487696</v>
+        <v>0.1408102271762508</v>
       </c>
       <c r="J72" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.400404347435</v>
+        <v>0.4004149349557375</v>
       </c>
     </row>
     <row r="73">
@@ -3473,34 +3473,34 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>24.1929431201</v>
+        <v>24.20111197054516</v>
       </c>
       <c r="D73" t="n">
-        <v>7.72171604473</v>
+        <v>7.723273420138849</v>
       </c>
       <c r="E73" t="n">
-        <v>3.60399455348</v>
+        <v>3.604779886536615</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0580615805608</v>
+        <v>0.05118205845390425</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0247587392387</v>
+        <v>0.01965237335599148</v>
       </c>
       <c r="H73" t="n">
-        <v>49.9998265463</v>
+        <v>50.69744939134747</v>
       </c>
       <c r="I73" t="n">
-        <v>0.144472614529</v>
+        <v>0.1825100483052528</v>
       </c>
       <c r="J73" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0.400483487101</v>
+        <v>0.4004927330895087</v>
       </c>
     </row>
     <row r="74">
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>22.5165963302</v>
+        <v>22.52362618917236</v>
       </c>
       <c r="D74" t="n">
-        <v>6.88408068308</v>
+        <v>6.885258587817762</v>
       </c>
       <c r="E74" t="n">
-        <v>3.071510722</v>
+        <v>3.07201301344049</v>
       </c>
       <c r="F74" t="n">
-        <v>4.27688846705</v>
+        <v>4.271341838841741</v>
       </c>
       <c r="G74" t="n">
-        <v>0.812491290343</v>
+        <v>0.8071669476483727</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0375224238591</v>
+        <v>0.03752242385914702</v>
       </c>
       <c r="I74" t="n">
-        <v>0.24152760822</v>
+        <v>0.27367813267745</v>
       </c>
       <c r="J74" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.394016782355</v>
+        <v>0.3940236692089303</v>
       </c>
     </row>
     <row r="75">
@@ -3557,34 +3557,34 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>22.9253630441</v>
+        <v>22.92536304412692</v>
       </c>
       <c r="D75" t="n">
-        <v>6.99960090263</v>
+        <v>7.000901625953572</v>
       </c>
       <c r="E75" t="n">
-        <v>3.12153754182</v>
+        <v>3.122096140917449</v>
       </c>
       <c r="F75" t="n">
-        <v>3.1123443642</v>
+        <v>3.106034205241497</v>
       </c>
       <c r="G75" t="n">
-        <v>0.812952234856</v>
+        <v>0.8076176256888105</v>
       </c>
       <c r="H75" t="n">
-        <v>11.3352503009</v>
+        <v>11.52846198761585</v>
       </c>
       <c r="I75" t="n">
-        <v>0.245409522089</v>
+        <v>0.2730951658062835</v>
       </c>
       <c r="J75" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.395038096987</v>
+        <v>0.3950457027877508</v>
       </c>
     </row>
     <row r="76">
@@ -3599,34 +3599,34 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>23.5500176644</v>
+        <v>23.55001766437313</v>
       </c>
       <c r="D76" t="n">
-        <v>7.38177798153</v>
+        <v>7.383327166986112</v>
       </c>
       <c r="E76" t="n">
-        <v>3.38489265958</v>
+        <v>3.385648684752626</v>
       </c>
       <c r="F76" t="n">
-        <v>1.73466299105</v>
+        <v>1.727586108833671</v>
       </c>
       <c r="G76" t="n">
-        <v>0.813891833691</v>
+        <v>0.8085349025917852</v>
       </c>
       <c r="H76" t="n">
-        <v>1.19702761728</v>
+        <v>1.320596137472795</v>
       </c>
       <c r="I76" t="n">
-        <v>0.216579096707</v>
+        <v>0.2416402229766913</v>
       </c>
       <c r="J76" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.397866646454</v>
+        <v>0.3978760698288937</v>
       </c>
     </row>
     <row r="77">
@@ -3641,34 +3641,34 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>23.6318628577</v>
+        <v>23.62654162789718</v>
       </c>
       <c r="D77" t="n">
-        <v>7.49136430727</v>
+        <v>7.487295760891283</v>
       </c>
       <c r="E77" t="n">
-        <v>3.48172729149</v>
+        <v>3.479628360293456</v>
       </c>
       <c r="F77" t="n">
-        <v>1.28065798807</v>
+        <v>1.297421243907116</v>
       </c>
       <c r="G77" t="n">
-        <v>0.82633119926</v>
+        <v>0.8358329730959437</v>
       </c>
       <c r="H77" t="n">
-        <v>16.9832369556</v>
+        <v>15.47899516292579</v>
       </c>
       <c r="I77" t="n">
-        <v>0.17896225561</v>
+        <v>0.3024139413974242</v>
       </c>
       <c r="J77" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0.399178442441</v>
+        <v>0.3991446042778304</v>
       </c>
     </row>
     <row r="78">
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>25.0046881423</v>
+        <v>25.00468814230315</v>
       </c>
       <c r="D78" t="n">
-        <v>8.072234738060001</v>
+        <v>8.078376937099035</v>
       </c>
       <c r="E78" t="n">
-        <v>3.78463867441</v>
+        <v>3.787677651696431</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.90768735957</v>
+        <v>-1.937115995218944</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.67204393117</v>
+        <v>-1.697661034957823</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>99.95706343848207</v>
       </c>
       <c r="I78" t="n">
-        <v>0.060181347228</v>
+        <v>0.1384900875608106</v>
       </c>
       <c r="J78" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0.40127336341</v>
+        <v>0.4012937648345138</v>
       </c>
     </row>
     <row r="79">
@@ -3725,34 +3725,34 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>23.557174764</v>
+        <v>23.57882188384849</v>
       </c>
       <c r="D79" t="n">
-        <v>7.2139759676</v>
+        <v>7.220258206114341</v>
       </c>
       <c r="E79" t="n">
-        <v>3.23501058222</v>
+        <v>3.238014283992043</v>
       </c>
       <c r="F79" t="n">
-        <v>2.2645086212</v>
+        <v>2.231718112754426</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.892007006228</v>
+        <v>-0.9186932610070743</v>
       </c>
       <c r="H79" t="n">
-        <v>5.37975407431</v>
+        <v>5.705048065388222</v>
       </c>
       <c r="I79" t="n">
-        <v>0.167166011201</v>
+        <v>0.2084926332581718</v>
       </c>
       <c r="J79" t="n">
-        <v>1.55431223448e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.394759663493</v>
+        <v>0.3947834116307594</v>
       </c>
     </row>
     <row r="80">
@@ -3767,34 +3767,34 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>24.0517869305</v>
+        <v>24.08555266842837</v>
       </c>
       <c r="D80" t="n">
-        <v>7.33697819912</v>
+        <v>7.343367157824325</v>
       </c>
       <c r="E80" t="n">
-        <v>3.28835605326</v>
+        <v>3.291397138584248</v>
       </c>
       <c r="F80" t="n">
-        <v>1.11228157105</v>
+        <v>1.080054456720852</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.891597047049</v>
+        <v>-0.9182878695459887</v>
       </c>
       <c r="H80" t="n">
-        <v>29.9447701281</v>
+        <v>30.03681631766831</v>
       </c>
       <c r="I80" t="n">
-        <v>0.176360499171</v>
+        <v>0.1737903794924142</v>
       </c>
       <c r="J80" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0.395787942421</v>
+        <v>0.3958111886967983</v>
       </c>
     </row>
     <row r="81">
@@ -3809,34 +3809,34 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>24.4413624382</v>
+        <v>24.45347239312542</v>
       </c>
       <c r="D81" t="n">
-        <v>7.72464722766</v>
+        <v>7.731052429311801</v>
       </c>
       <c r="E81" t="n">
-        <v>3.55843070076</v>
+        <v>3.561552993677634</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.24786360859</v>
+        <v>-0.2793212948428615</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.889064022726</v>
+        <v>-0.9157701747031236</v>
       </c>
       <c r="H81" t="n">
-        <v>46.9266296159</v>
+        <v>48.22475941501799</v>
       </c>
       <c r="I81" t="n">
-        <v>0.144822742375</v>
+        <v>0.126145625589559</v>
       </c>
       <c r="J81" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.398633281591</v>
+        <v>0.398656153779096</v>
       </c>
     </row>
     <row r="82">
@@ -3851,34 +3851,34 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>24.4759450361</v>
+        <v>24.4759450360823</v>
       </c>
       <c r="D82" t="n">
-        <v>7.83323733454</v>
+        <v>7.835295244259287</v>
       </c>
       <c r="E82" t="n">
-        <v>3.65609093789</v>
+        <v>3.657114384821787</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.7007513088839999</v>
+        <v>-0.7135897329000426</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.87952409444</v>
+        <v>-0.8914094406123058</v>
       </c>
       <c r="H82" t="n">
-        <v>85.2780698631</v>
+        <v>85.96274543960348</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0932846934654</v>
+        <v>0.1646904648671359</v>
       </c>
       <c r="J82" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0.399938332071</v>
+        <v>0.3999368157924055</v>
       </c>
     </row>
     <row r="83">
@@ -3893,34 +3893,34 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>25.0046881423</v>
+        <v>25.01250723169329</v>
       </c>
       <c r="D83" t="n">
-        <v>8.07265394099</v>
+        <v>8.078815079750363</v>
       </c>
       <c r="E83" t="n">
-        <v>3.78485133496</v>
+        <v>3.787900676456809</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.90934186265</v>
+        <v>-1.938846615319829</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.67318123262</v>
+        <v>-1.698849844114964</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>99.94479773855673</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0615021037902</v>
+        <v>0.1393067720580608</v>
       </c>
       <c r="J83" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.401276212687</v>
+        <v>0.4012967612268616</v>
       </c>
     </row>
     <row r="84">
@@ -3935,34 +3935,34 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>23.557174764</v>
+        <v>23.57882188384849</v>
       </c>
       <c r="D84" t="n">
-        <v>7.2140479386</v>
+        <v>7.220404320520414</v>
       </c>
       <c r="E84" t="n">
-        <v>3.23505020232</v>
+        <v>3.238100155232956</v>
       </c>
       <c r="F84" t="n">
-        <v>1.84525583546</v>
+        <v>1.812379276108534</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.9713233371160001</v>
+        <v>-0.9980235391882749</v>
       </c>
       <c r="H84" t="n">
-        <v>7.39782096969</v>
+        <v>7.702102713270881</v>
       </c>
       <c r="I84" t="n">
-        <v>0.157096350928</v>
+        <v>0.1986719019311989</v>
       </c>
       <c r="J84" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>5.329070518200751e-15</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.394760203449</v>
+        <v>0.3947845279445985</v>
       </c>
     </row>
     <row r="85">
@@ -3977,34 +3977,34 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>24.0517869305</v>
+        <v>24.08555266842837</v>
       </c>
       <c r="D85" t="n">
-        <v>7.33703783671</v>
+        <v>7.343487908497512</v>
       </c>
       <c r="E85" t="n">
-        <v>3.2883832354</v>
+        <v>3.29146393416658</v>
       </c>
       <c r="F85" t="n">
-        <v>0.808437315882</v>
+        <v>0.7761772891011671</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.97091739129</v>
+        <v>-0.9976174356039372</v>
       </c>
       <c r="H85" t="n">
-        <v>30.9686940534</v>
+        <v>31.11524287917255</v>
       </c>
       <c r="I85" t="n">
-        <v>0.164231576247</v>
+        <v>0.1641090056815877</v>
       </c>
       <c r="J85" t="n">
-        <v>4.4408920985e-16</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.39578835809</v>
+        <v>0.3958120642124063</v>
       </c>
     </row>
     <row r="86">
@@ -4019,34 +4019,34 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>24.4413624382</v>
+        <v>24.45347239312542</v>
       </c>
       <c r="D86" t="n">
-        <v>7.72474988431</v>
+        <v>7.731183495370551</v>
       </c>
       <c r="E86" t="n">
-        <v>3.55847484599</v>
+        <v>3.561614591053933</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.415536207098</v>
+        <v>-0.4469790343645172</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.968557457393</v>
+        <v>-0.9952607748502016</v>
       </c>
       <c r="H86" t="n">
-        <v>54.5532535806</v>
+        <v>56.103873233827</v>
       </c>
       <c r="I86" t="n">
-        <v>0.136159765026</v>
+        <v>0.1212253918559058</v>
       </c>
       <c r="J86" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.398633954815</v>
+        <v>0.3986570411343084</v>
       </c>
     </row>
     <row r="87">
@@ -4061,34 +4061,1294 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>24.4759450361</v>
+        <v>24.4759450360823</v>
       </c>
       <c r="D87" t="n">
-        <v>7.83381662796</v>
+        <v>7.835895213132503</v>
       </c>
       <c r="E87" t="n">
-        <v>3.65638387092</v>
+        <v>3.657417658007697</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.703091646905</v>
+        <v>-0.7160148336489793</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.881111257089</v>
+        <v>-0.893054988761786</v>
       </c>
       <c r="H87" t="n">
-        <v>85.024899408</v>
+        <v>85.79907123733406</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0951022213208</v>
+        <v>0.1663486893538007</v>
       </c>
       <c r="J87" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.399942424002</v>
+        <v>0.399941048335793</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>25.00468814230315</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8.072653940990618</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.784851334964232</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-1.90934186264575</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-1.673181232614196</v>
+      </c>
+      <c r="H88" t="n">
+        <v>100</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.06150210378844483</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.4012762126872234</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>23.55717476400687</v>
+      </c>
+      <c r="D89" t="n">
+        <v>7.214569213695305</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3.235306185985363</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.261885658333481</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-0.8936123490653419</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.393467554056205</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.1687187991926389</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.3947640107937305</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>24.05178693046021</v>
+      </c>
+      <c r="D90" t="n">
+        <v>7.337569840258362</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.288649194136632</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.109762470654366</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-0.8932020649779404</v>
+      </c>
+      <c r="H90" t="n">
+        <v>29.94669071348114</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.1776368940282172</v>
+      </c>
+      <c r="J90" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.3957921517848939</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>24.44136243821318</v>
+      </c>
+      <c r="D91" t="n">
+        <v>7.725232752068688</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3.558723650054411</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-0.2502572354662158</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-0.8906680605969928</v>
+      </c>
+      <c r="H91" t="n">
+        <v>47.21183843118668</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.1461453158657377</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.3986373490433299</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>24.4759450360823</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7.833816627962777</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3.656383870924486</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-0.7030916469060574</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-0.8811112570897109</v>
+      </c>
+      <c r="H92" t="n">
+        <v>85.02489940797254</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.09510222132070821</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1.332267629550188e-15</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.3999424240017284</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>24.98241890212723</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8.064696552565302</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.780930740770621</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-1.870965542556647</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-1.639474625984119</v>
+      </c>
+      <c r="H93" t="n">
+        <v>100</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.2136945522824886</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.401251366985059</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>23.50384221817591</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7.206807997432006</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.231639042600924</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.302995777797023</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-0.8586657628397245</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5.111605158430353</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.3203440591020467</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.3947373856668956</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>23.99551913066821</v>
+      </c>
+      <c r="D95" t="n">
+        <v>7.32960600949519</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3.284898606432643</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.15073325871316</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-0.8582430053838228</v>
+      </c>
+      <c r="H95" t="n">
+        <v>29.78018452692786</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.3335886650454152</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.3957655581012645</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>24.42156888645965</v>
+      </c>
+      <c r="D96" t="n">
+        <v>7.717013632118741</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.554750045505808</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-0.2096319852768704</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-0.8556731877140156</v>
+      </c>
+      <c r="H96" t="n">
+        <v>45.50880041238882</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.3102789106210376</v>
+      </c>
+      <c r="J96" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.398609915176781</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>24.46751575879926</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7.831703715829001</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.655393520427864</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-0.6896242785737857</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-0.8671115167000188</v>
+      </c>
+      <c r="H97" t="n">
+        <v>84.4043844208578</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.1675126722567095</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.332267629550188e-15</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.3999488446947563</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>25.00468814230315</v>
+      </c>
+      <c r="D98" t="n">
+        <v>8.077039855600278</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3.787005393623441</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-1.930601403625839</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-1.691950536204567</v>
+      </c>
+      <c r="H98" t="n">
+        <v>99.95706343848207</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.128397122925088</v>
+      </c>
+      <c r="J98" t="n">
+        <v>3.552713678800501e-15</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.4012895069196065</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>23.57882188384849</v>
+      </c>
+      <c r="D99" t="n">
+        <v>7.218848109461414</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3.237299374210063</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.239286629266906</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-0.9130394738420903</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.614280072094905</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2103736006198455</v>
+      </c>
+      <c r="J99" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.3947780277589596</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>24.08555266842837</v>
+      </c>
+      <c r="D100" t="n">
+        <v>7.34196980655752</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3.290691536583922</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.087191436525852</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-0.9126362416043808</v>
+      </c>
+      <c r="H100" t="n">
+        <v>30.05237948231088</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.188352831377674</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.3958062040009862</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>24.45810075345599</v>
+      </c>
+      <c r="D101" t="n">
+        <v>7.729756050561401</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3.560899289674988</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-0.2726982481606725</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-0.9101233092584343</v>
+      </c>
+      <c r="H101" t="n">
+        <v>47.96798350873183</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.1449749724020424</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.3986519842721314</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>24.4759450360823</v>
+      </c>
+      <c r="D102" t="n">
+        <v>7.83542787691472</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3.657159907044961</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-0.7129530830879407</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-0.8905373561209721</v>
+      </c>
+      <c r="H102" t="n">
+        <v>85.50500507571714</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.1662756054218332</v>
+      </c>
+      <c r="J102" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.3999409343179154</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>25.00468814230315</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8.074581762398729</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3.785766856784445</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-1.919192330622804</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-1.682422425070936</v>
+      </c>
+      <c r="H103" t="n">
+        <v>100</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.1509244907077652</v>
+      </c>
+      <c r="J103" t="n">
+        <v>3.552713678800501e-15</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.401279417571007</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>23.57882188384849</v>
+      </c>
+      <c r="D104" t="n">
+        <v>7.216065752734587</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3.235901316368773</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.253397572933504</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-0.9029423179927366</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5.421521583203002</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.2437408541837382</v>
+      </c>
+      <c r="J104" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.3947644490930493</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>24.07354893221787</v>
+      </c>
+      <c r="D105" t="n">
+        <v>7.339204025086598</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3.289308005541165</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.100598650439784</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-0.902542588811845</v>
+      </c>
+      <c r="H105" t="n">
+        <v>29.93320732797929</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.2328707873376614</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.332267629550188e-15</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.3957933378837544</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>24.44978267583379</v>
+      </c>
+      <c r="D106" t="n">
+        <v>7.72712488866357</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3.559578391268648</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-0.260132307432206</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-0.9000378214524448</v>
+      </c>
+      <c r="H106" t="n">
+        <v>47.48035228235956</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.1937181069070783</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.3986403464687498</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>24.4759450360823</v>
+      </c>
+      <c r="D107" t="n">
+        <v>7.834815427080685</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3.656821040150833</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-0.7088740113108434</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-0.8871692795489031</v>
+      </c>
+      <c r="H107" t="n">
+        <v>85.09128981891784</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.1876681334588558</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.3999409703639418</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>25.03831705157468</v>
+      </c>
+      <c r="D108" t="n">
+        <v>8.07927478421974</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3.78811282401916</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-1.941229738605026</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-1.701193536250613</v>
+      </c>
+      <c r="H108" t="n">
+        <v>99.94479773855673</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.1693833726139113</v>
+      </c>
+      <c r="J108" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.4012970927615809</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>23.57882188384849</v>
+      </c>
+      <c r="D109" t="n">
+        <v>7.221049724235204</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.23833750236142</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.227875123445251</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-0.9226455495622027</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5.770471386199129</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.2373956439881807</v>
+      </c>
+      <c r="J109" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.3947861655107849</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>24.08555266842837</v>
+      </c>
+      <c r="D110" t="n">
+        <v>7.344233656116187</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.291752866130329</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.075813736429867</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-0.9222459941794177</v>
+      </c>
+      <c r="H110" t="n">
+        <v>30.06239298366212</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.1999120728998551</v>
+      </c>
+      <c r="J110" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.3958143262739848</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>24.45347239312542</v>
+      </c>
+      <c r="D111" t="n">
+        <v>7.732075728183053</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.562024918342473</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-0.2839817957924096</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-0.919743241813862</v>
+      </c>
+      <c r="H111" t="n">
+        <v>48.25245291024628</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.1540851866648323</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.332267629550188e-15</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.3986603494986449</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>24.4759450360823</v>
+      </c>
+      <c r="D112" t="n">
+        <v>7.836336669310874</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3.657614110449961</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-0.7182593923387214</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-0.8953099153188609</v>
+      </c>
+      <c r="H112" t="n">
+        <v>85.74133148479702</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.199197963140843</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.399941485525092</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>25.00468814230315</v>
+      </c>
+      <c r="D113" t="n">
+        <v>8.077913265674146</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3.787484290115068</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-1.934148863644692</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-1.694204886357616</v>
+      </c>
+      <c r="H113" t="n">
+        <v>99.95706343848207</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.1321400749207346</v>
+      </c>
+      <c r="J113" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.4012962227749131</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>23.57882188384849</v>
+      </c>
+      <c r="D114" t="n">
+        <v>7.22046294662703</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3.238245261972833</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.231577906344652</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-0.9157934013705831</v>
+      </c>
+      <c r="H114" t="n">
+        <v>5.597338709047843</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.2020619305841769</v>
+      </c>
+      <c r="J114" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.3947910043887213</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>24.08555266842837</v>
+      </c>
+      <c r="D115" t="n">
+        <v>7.343438485366194</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.291562691058986</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.080889949018245</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-0.9153758934253581</v>
+      </c>
+      <c r="H115" t="n">
+        <v>30.03681631766831</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.1864871442326104</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.332267629550188e-15</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.3958177185607155</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>24.45347239312542</v>
+      </c>
+      <c r="D116" t="n">
+        <v>7.730833649228214</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3.56151654826134</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-0.2774193395379431</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-0.9128264909681897</v>
+      </c>
+      <c r="H116" t="n">
+        <v>48.11672906362988</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.1437692023282248</v>
+      </c>
+      <c r="J116" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.3986604633448849</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>24.4759450360823</v>
+      </c>
+      <c r="D117" t="n">
+        <v>7.835026881523762</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3.657031392496298</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.7115777868824156</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-0.8885781613564695</v>
+      </c>
+      <c r="H117" t="n">
+        <v>85.89945317091488</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.155315249357242</v>
+      </c>
+      <c r="J117" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3999403045628327</v>
       </c>
     </row>
   </sheetData>
@@ -4102,7 +5362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4541,7 +5801,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>One row per configuration–policy combination: 17 configurations × 5 shock/policy outcomes, plus one benchmark row.</t>
+          <t>One row per configuration–policy combination: each structural or consumption-preference configuration has five shock/policy outcomes, plus one common benchmark row.</t>
         </is>
       </c>
     </row>
@@ -4812,70 +6072,142 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Policy: baseline</t>
+          <t>Scenario: consumption_CD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unshocked benchmark equilibrium, without the new support programme.</t>
+          <t>Cobb-Douglas consumption (elasticity 1) in both CGE and microsimulation; all other main settings unchanged.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Policy: shock</t>
+          <t>Scenario: consumption_flat_CES2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>No-policy reference equilibrium under the external price shock specified by case.</t>
+          <t>Single-level CES consumption with elasticity 2 in CGE and microsimulation.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Policy: perfect_targeting</t>
+          <t>Scenario: upper_substitution_050</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+          <t>Food-energy-other upper-nest elasticity is 0.50; within-nest elasticities retain their main values.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Policy: pmt</t>
+          <t>Scenario: upper_substitution_085</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+          <t>Food-energy-other upper-nest elasticity is 0.85; within-nest elasticities retain their main values.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Policy: universal_cash</t>
+          <t>Scenario: low_within_substitution</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Universal cash: equal per-person payment to every represented person.</t>
+          <t>Within-nest elasticities are food 0.25, energy 0.20 and other 0.25; upper-nest elasticity remains 0.25.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Scenario: high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Within-nest elasticities are food 1.00, energy 0.80 and other 1.00; upper-nest elasticity remains 0.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Policy: baseline</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unshocked benchmark equilibrium, without the new support programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Policy: shock</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>No-policy reference equilibrium under the external price shock specified by case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Policy: perfect_targeting</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Policy: pmt</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Policy: universal_cash</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Universal cash: equal per-person payment to every represented person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Policy: price_support</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Price support: a common proportional discount on eligible household purchases, solved at the same final net fiscal cost.</t>
         </is>
